--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -384,6 +384,9 @@
     <t>ARCADIO</t>
   </si>
   <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -474,6 +477,9 @@
     <t>ANA LILIANA</t>
   </si>
   <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
     <t>VENUS</t>
   </si>
   <si>
@@ -562,12 +568,6 @@
   </si>
   <si>
     <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1138,7 +1138,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1227,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1253,7 +1253,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1316,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1342,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>8</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1561,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1624,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1650,7 +1650,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1713,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1739,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -1802,7 +1802,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>8</v>
@@ -1828,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -1891,7 +1891,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>7</v>
@@ -1917,7 +1917,7 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1980,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -2006,7 +2006,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -2069,7 +2069,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -2095,7 +2095,7 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2158,7 +2158,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2184,7 +2184,7 @@
         <v>9</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -2247,7 +2247,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>9</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -2336,7 +2336,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -2362,7 +2362,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2425,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2451,7 +2451,7 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -2514,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2540,7 +2540,7 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -2603,7 +2603,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2629,7 +2629,7 @@
         <v>9</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -2692,7 +2692,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>6</v>
@@ -2718,7 +2718,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -2870,7 +2870,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>10</v>
@@ -2959,7 +2959,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -3048,7 +3048,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -3074,7 +3074,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>10</v>
@@ -3137,7 +3137,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -3163,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -3226,7 +3226,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3252,7 +3252,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -3315,7 +3315,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>8</v>
@@ -3341,7 +3341,7 @@
         <v>10</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>9</v>
@@ -3404,7 +3404,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3430,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -3493,7 +3493,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3519,7 +3519,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>9</v>
@@ -3582,7 +3582,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>9</v>
@@ -3608,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>10</v>
@@ -3671,7 +3671,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>10</v>
@@ -3697,7 +3697,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -3760,7 +3760,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>8</v>
@@ -3786,7 +3786,7 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>10</v>
@@ -3849,7 +3849,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>10</v>
@@ -3875,7 +3875,7 @@
         <v>9</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E36">
         <v>8</v>
@@ -3938,7 +3938,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>8</v>
@@ -3964,7 +3964,7 @@
         <v>9</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>8</v>
@@ -4027,7 +4027,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <v>8</v>
@@ -4053,7 +4053,7 @@
         <v>10</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E38">
         <v>9</v>
@@ -4116,7 +4116,7 @@
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -4142,7 +4142,7 @@
         <v>9</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -4205,7 +4205,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z39">
         <v>5</v>
@@ -4231,7 +4231,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E40">
         <v>10</v>
@@ -4294,7 +4294,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z40">
         <v>10</v>
@@ -4320,7 +4320,7 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E41">
         <v>5</v>
@@ -4383,7 +4383,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z41">
         <v>5</v>
@@ -4409,7 +4409,7 @@
         <v>9</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -4472,7 +4472,7 @@
         <v>9</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z42">
         <v>6</v>
@@ -4498,7 +4498,7 @@
         <v>9</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -4561,7 +4561,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z43">
         <v>5</v>
@@ -4587,7 +4587,7 @@
         <v>10</v>
       </c>
       <c r="D44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E44">
         <v>7</v>
@@ -4650,7 +4650,7 @@
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z44">
         <v>7</v>
@@ -4676,7 +4676,7 @@
         <v>9</v>
       </c>
       <c r="D45">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E45">
         <v>5</v>
@@ -4739,7 +4739,7 @@
         <v>9</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z45">
         <v>5</v>
@@ -4887,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>106.7</v>
@@ -4955,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>106.7</v>
@@ -5023,7 +5023,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>106.7</v>
@@ -5091,7 +5091,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>106.7</v>
@@ -5191,7 +5191,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>106.7</v>
@@ -5259,7 +5259,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>106.7</v>
@@ -5327,7 +5327,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>106.7</v>
@@ -5395,7 +5395,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>106.7</v>
@@ -5463,7 +5463,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>106.7</v>
@@ -5531,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>106.7</v>
@@ -5599,7 +5599,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>106.7</v>
@@ -5667,7 +5667,7 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>106.7</v>
@@ -5735,7 +5735,7 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>106.7</v>
@@ -5803,7 +5803,7 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>106.7</v>
@@ -5871,7 +5871,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>106.7</v>
@@ -5939,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>106.7</v>
@@ -6007,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>106.7</v>
@@ -6075,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>106.7</v>
@@ -6143,7 +6143,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>106.7</v>
@@ -6211,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>106.7</v>
@@ -6279,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>106.7</v>
@@ -6347,7 +6347,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>106.7</v>
@@ -6415,7 +6415,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>106.7</v>
@@ -6483,7 +6483,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>106.7</v>
@@ -6551,7 +6551,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>106.7</v>
@@ -6619,7 +6619,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>106.7</v>
@@ -6687,7 +6687,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>106.7</v>
@@ -6755,7 +6755,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>106.7</v>
@@ -6823,7 +6823,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>106.7</v>
@@ -6891,7 +6891,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>106.7</v>
@@ -6959,7 +6959,7 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>106.7</v>
@@ -7027,7 +7027,7 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>106.7</v>
@@ -7095,7 +7095,7 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>106.7</v>
@@ -7163,7 +7163,7 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>106.7</v>
@@ -7231,7 +7231,7 @@
         <v>100</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>106.7</v>
@@ -7299,7 +7299,7 @@
         <v>100</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E40">
         <v>106.7</v>
@@ -7367,7 +7367,7 @@
         <v>100</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41">
         <v>106.7</v>
@@ -7435,7 +7435,7 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42">
         <v>106.7</v>
@@ -7503,7 +7503,7 @@
         <v>100</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>106.7</v>
@@ -7571,7 +7571,7 @@
         <v>100</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>106.7</v>
@@ -7639,7 +7639,7 @@
         <v>100</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45">
         <v>106.7</v>
@@ -7748,7 +7748,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -7757,27 +7757,30 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>78.05</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>21.95</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7786,19 +7789,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>78.05</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="G3">
-        <v>21.95</v>
+        <v>9.76</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7974,7 +7977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7999,823 +8002,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920252</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920253</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920254</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920256</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920257</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920258</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920259</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920081</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920262</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920263</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920264</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920266</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920267</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920087</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920088</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920358</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920268</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920091</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920270</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920271</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" t="s">
-        <v>160</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920272</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920273</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" t="s">
-        <v>162</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920274</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920361</v>
-      </c>
-      <c r="B26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920275</v>
-      </c>
-      <c r="B27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920362</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" t="s">
-        <v>166</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920276</v>
-      </c>
-      <c r="B29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" t="s">
-        <v>167</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920277</v>
-      </c>
-      <c r="B30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" t="s">
-        <v>168</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920278</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051420149</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" t="s">
-        <v>170</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920279</v>
-      </c>
-      <c r="B33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920280</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" t="s">
-        <v>172</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920106</v>
-      </c>
-      <c r="B35" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920282</v>
-      </c>
-      <c r="B36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920284</v>
-      </c>
-      <c r="B37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" t="s">
-        <v>175</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920285</v>
-      </c>
-      <c r="B38" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>176</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920286</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" t="s">
-        <v>94</v>
-      </c>
-      <c r="D39" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920358</v>
-      </c>
-      <c r="B40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40" t="s">
-        <v>178</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920287</v>
-      </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" t="s">
-        <v>139</v>
-      </c>
-      <c r="D41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920288</v>
-      </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" t="s">
-        <v>180</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -8860,10 +8046,10 @@
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8877,10 +8063,10 @@
         <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8894,10 +8080,10 @@
         <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8911,10 +8097,10 @@
         <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8928,10 +8114,10 @@
         <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8945,10 +8131,10 @@
         <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8962,10 +8148,10 @@
         <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8979,10 +8165,10 @@
         <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8996,10 +8182,10 @@
         <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9013,545 +8199,545 @@
         <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920263</v>
+        <v>19330051920155</v>
       </c>
       <c r="B12" t="s">
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920264</v>
+        <v>21330051920263</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920266</v>
+        <v>21330051920264</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920267</v>
+        <v>21330051920266</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920087</v>
+        <v>21330051920267</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920088</v>
+        <v>21330051920087</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
         <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920358</v>
+        <v>21330051920088</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
         <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920268</v>
+        <v>21330051920358</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
         <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920091</v>
+        <v>21330051920268</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920270</v>
+        <v>21330051920091</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920271</v>
+        <v>21330051920270</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
         <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920272</v>
+        <v>21330051920271</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
         <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920273</v>
+        <v>21330051920272</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
         <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920274</v>
+        <v>21330051920273</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920361</v>
+        <v>21330051920274</v>
       </c>
       <c r="B26" t="s">
         <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920275</v>
+        <v>21330051920361</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
         <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920362</v>
+        <v>21330051920275</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920276</v>
+        <v>21330051920362</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
         <v>131</v>
       </c>
       <c r="D29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920277</v>
+        <v>21330051920276</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
         <v>132</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920278</v>
+        <v>21330051920277</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051420149</v>
+        <v>21330051920278</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920279</v>
+        <v>21330051420149</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
         <v>134</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920280</v>
+        <v>21330051920279</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920106</v>
+        <v>21330051920280</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920282</v>
+        <v>21330051920106</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
         <v>136</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920284</v>
+        <v>21330051920282</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
         <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920285</v>
+        <v>21330051920284</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920286</v>
+        <v>21330051920285</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>20330051920358</v>
+        <v>21330051920286</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920287</v>
+        <v>20330051920358</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
         <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920288</v>
+        <v>21330051920287</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>19330051920155</v>
+        <v>21330051920288</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -9567,7 +8753,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9599,16 +8785,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920251</v>
+        <v>21330051920253</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -9622,39 +8808,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920251</v>
+        <v>21330051920253</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>67</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920257</v>
+        <v>21330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -9663,21 +8849,21 @@
         <v>67</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920257</v>
+        <v>21330051920088</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -9691,39 +8877,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920088</v>
+        <v>21330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920088</v>
+        <v>21330051920257</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -9737,25 +8923,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920358</v>
+        <v>19330051920155</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -9766,10 +8952,10 @@
         <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -9792,30 +8978,30 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>67</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920286</v>
+        <v>20330051920358</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -9825,785 +9011,6 @@
       </c>
       <c r="G11">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920358</v>
-      </c>
-      <c r="B12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" t="s">
-        <v>178</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920358</v>
-      </c>
-      <c r="B13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920254</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920256</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920258</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920081</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920262</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920155</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" t="s">
-        <v>182</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920263</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>144</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920264</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920266</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920267</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920087</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920268</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920091</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920270</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920271</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920272</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920273</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920274</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>163</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920361</v>
-      </c>
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" t="s">
-        <v>164</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920275</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920362</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" t="s">
-        <v>166</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920276</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" t="s">
-        <v>167</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920277</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920278</v>
-      </c>
-      <c r="B38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" t="s">
-        <v>169</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051420149</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" t="s">
-        <v>170</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920279</v>
-      </c>
-      <c r="B40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>67</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920280</v>
-      </c>
-      <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920106</v>
-      </c>
-      <c r="B42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" t="s">
-        <v>135</v>
-      </c>
-      <c r="D42" t="s">
-        <v>173</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>67</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920284</v>
-      </c>
-      <c r="B43" t="s">
-        <v>107</v>
-      </c>
-      <c r="C43" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" t="s">
-        <v>175</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>67</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920285</v>
-      </c>
-      <c r="B44" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44" t="s">
-        <v>176</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920288</v>
-      </c>
-      <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" t="s">
-        <v>180</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>67</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -222,10 +222,25 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
     <t>NC</t>
@@ -7783,7 +7798,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>41</v>
@@ -7815,7 +7830,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>41</v>
@@ -7847,7 +7862,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>42</v>
@@ -7879,7 +7894,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>42</v>
@@ -7911,7 +7926,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>41</v>
@@ -7943,7 +7958,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8">
         <v>42</v>
@@ -7986,16 +8001,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8020,16 +8035,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>65</v>
@@ -8040,13 +8055,13 @@
         <v>21330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -8057,13 +8072,13 @@
         <v>21330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -8074,13 +8089,13 @@
         <v>21330051920253</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -8091,13 +8106,13 @@
         <v>21330051920254</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -8108,13 +8123,13 @@
         <v>21330051920256</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -8125,13 +8140,13 @@
         <v>21330051920257</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8142,13 +8157,13 @@
         <v>21330051920258</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -8159,13 +8174,13 @@
         <v>21330051920259</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -8176,13 +8191,13 @@
         <v>21330051920081</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -8193,13 +8208,13 @@
         <v>21330051920262</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -8210,13 +8225,13 @@
         <v>19330051920155</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -8227,13 +8242,13 @@
         <v>21330051920263</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -8244,13 +8259,13 @@
         <v>21330051920264</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -8261,13 +8276,13 @@
         <v>21330051920266</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -8278,10 +8293,10 @@
         <v>21330051920267</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -8292,13 +8307,13 @@
         <v>21330051920087</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -8309,13 +8324,13 @@
         <v>21330051920088</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -8326,13 +8341,13 @@
         <v>21330051920358</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -8343,13 +8358,13 @@
         <v>21330051920268</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -8360,13 +8375,13 @@
         <v>21330051920091</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -8377,13 +8392,13 @@
         <v>21330051920270</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -8394,13 +8409,13 @@
         <v>21330051920271</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -8411,13 +8426,13 @@
         <v>21330051920272</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -8428,13 +8443,13 @@
         <v>21330051920273</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -8445,13 +8460,13 @@
         <v>21330051920274</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -8462,13 +8477,13 @@
         <v>21330051920361</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -8479,13 +8494,13 @@
         <v>21330051920275</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -8496,13 +8511,13 @@
         <v>21330051920362</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -8513,13 +8528,13 @@
         <v>21330051920276</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -8530,13 +8545,13 @@
         <v>21330051920277</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -8547,13 +8562,13 @@
         <v>21330051920278</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -8564,13 +8579,13 @@
         <v>21330051420149</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -8581,13 +8596,13 @@
         <v>21330051920279</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -8598,13 +8613,13 @@
         <v>21330051920280</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -8615,13 +8630,13 @@
         <v>21330051920106</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -8632,13 +8647,13 @@
         <v>21330051920282</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D37" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -8649,13 +8664,13 @@
         <v>21330051920284</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D38" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -8666,13 +8681,13 @@
         <v>21330051920285</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -8683,13 +8698,13 @@
         <v>21330051920286</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -8700,13 +8715,13 @@
         <v>20330051920358</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -8717,13 +8732,13 @@
         <v>21330051920287</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -8734,13 +8749,13 @@
         <v>21330051920288</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -8762,16 +8777,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8788,19 +8803,19 @@
         <v>21330051920253</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8811,13 +8826,13 @@
         <v>21330051920253</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -8834,19 +8849,19 @@
         <v>21330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8857,13 +8872,13 @@
         <v>21330051920088</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -8880,19 +8895,19 @@
         <v>21330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8903,13 +8918,13 @@
         <v>21330051920257</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -8926,19 +8941,19 @@
         <v>19330051920155</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8949,13 +8964,13 @@
         <v>21330051920358</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -8972,13 +8987,13 @@
         <v>21330051920286</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -8995,13 +9010,13 @@
         <v>20330051920358</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>

--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -231,12 +230,12 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -255,340 +254,76 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>RUBALCAVA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
     <t>AMECA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
   </si>
   <si>
     <t>YARELI</t>
   </si>
   <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>BIBIAN YANEL</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>EVELIN ALEXANDRA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
   </si>
   <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>ANA PAOLA</t>
-  </si>
-  <si>
-    <t>ALYN</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MILDRED MARIANA</t>
-  </si>
-  <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGELICA NAOMI</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>BRYAN ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>BRIANDA RENEE</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
     <t>MAGDA SARAY</t>
   </si>
   <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
     <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -641,11 +376,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1114,16 +850,16 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1156,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1203,16 +939,16 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1251,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1292,16 +1028,16 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1337,10 +1073,10 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1381,16 +1117,16 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1423,7 +1159,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1449,13 +1185,13 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1467,7 +1203,7 @@
         <v>-1</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1511,16 +1247,16 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1553,13 +1289,13 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA9">
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1600,16 +1336,16 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1642,16 +1378,16 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1689,16 +1425,16 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1734,13 +1470,13 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1778,16 +1514,16 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1820,13 +1556,13 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1867,16 +1603,16 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1912,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1956,16 +1692,16 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1998,7 +1734,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -2045,16 +1781,16 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2087,13 +1823,13 @@
         <v>6</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -2134,16 +1870,16 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2176,16 +1912,16 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2223,16 +1959,16 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2265,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17">
         <v>7</v>
@@ -2312,16 +2048,16 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2354,16 +2090,16 @@
         <v>7</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2401,16 +2137,16 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2443,7 +2179,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -2490,16 +2226,16 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2535,13 +2271,13 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2579,16 +2315,16 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2624,10 +2360,10 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2668,16 +2404,16 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2710,16 +2446,16 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2757,16 +2493,16 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2846,16 +2582,16 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2935,16 +2671,16 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2983,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -3024,16 +2760,16 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -3113,16 +2849,16 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3164,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3202,16 +2938,16 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3244,10 +2980,10 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3291,16 +3027,16 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3336,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>10</v>
@@ -3380,16 +3116,16 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3422,7 +3158,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3431,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3469,16 +3205,16 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3511,13 +3247,13 @@
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA31">
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3558,16 +3294,16 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3600,16 +3336,16 @@
         <v>6</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>8</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3647,16 +3383,16 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3736,16 +3472,16 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3778,7 +3514,7 @@
         <v>8</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>10</v>
@@ -3825,16 +3561,16 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3914,16 +3650,16 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3956,7 +3692,7 @@
         <v>7</v>
       </c>
       <c r="Z36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36">
         <v>10</v>
@@ -3965,7 +3701,7 @@
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -4003,16 +3739,16 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -4045,16 +3781,16 @@
         <v>8</v>
       </c>
       <c r="Z37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB37">
         <v>8</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -4092,16 +3828,16 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4137,13 +3873,13 @@
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB38">
         <v>9</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -4181,16 +3917,16 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4226,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB39">
         <v>7</v>
@@ -4270,16 +4006,16 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4315,13 +4051,13 @@
         <v>10</v>
       </c>
       <c r="AA40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4359,16 +4095,16 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4410,7 +4146,7 @@
         <v>8</v>
       </c>
       <c r="AC41">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -4448,16 +4184,16 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4496,7 +4232,7 @@
         <v>8</v>
       </c>
       <c r="AB42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>8</v>
@@ -4537,16 +4273,16 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4579,7 +4315,7 @@
         <v>7</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA43">
         <v>10</v>
@@ -4626,16 +4362,16 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -4668,16 +4404,16 @@
         <v>6</v>
       </c>
       <c r="Z44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44">
         <v>10</v>
       </c>
       <c r="AB44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC44">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:29">
@@ -4715,16 +4451,16 @@
         <v>-1</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P45">
         <v>-1</v>
@@ -4757,7 +4493,7 @@
         <v>5</v>
       </c>
       <c r="Z45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA45">
         <v>10</v>
@@ -4766,7 +4502,7 @@
         <v>9</v>
       </c>
       <c r="AC45">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4926,16 +4662,16 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -4994,16 +4730,16 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>114.3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -5062,16 +4798,16 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -5130,16 +4866,16 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -5177,13 +4913,13 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5230,16 +4966,16 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -5298,16 +5034,16 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -5366,16 +5102,16 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -5434,16 +5170,16 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -5502,16 +5238,16 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -5570,16 +5306,16 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -5638,16 +5374,16 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -5706,16 +5442,16 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -5774,16 +5510,16 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -5842,16 +5578,16 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5910,16 +5646,16 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5978,16 +5714,16 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -6046,16 +5782,16 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -6114,16 +5850,16 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>114.3</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -6182,16 +5918,16 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -6250,16 +5986,16 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -6318,16 +6054,16 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -6386,16 +6122,16 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -6454,16 +6190,16 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6522,16 +6258,16 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6590,16 +6326,16 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6658,16 +6394,16 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -6726,16 +6462,16 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -6794,16 +6530,16 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -6862,16 +6598,16 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -6930,16 +6666,16 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -6998,16 +6734,16 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -7066,16 +6802,16 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -7134,16 +6870,16 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -7202,16 +6938,16 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -7270,16 +7006,16 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>114.3</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -7338,16 +7074,16 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -7406,16 +7142,16 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -7474,16 +7210,16 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>114.3</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -7542,16 +7278,16 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -7610,16 +7346,16 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -7678,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -7727,6 +7463,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -7772,24 +7510,24 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>78.05</v>
-      </c>
-      <c r="G2">
-        <v>21.95</v>
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>17.1</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7809,11 +7547,11 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="F3">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="G3">
-        <v>9.76</v>
+      <c r="F3" s="2">
+        <v>90.2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -7821,7 +7559,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7841,11 +7579,11 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="G4">
-        <v>9.76</v>
+      <c r="F4" s="2">
+        <v>90.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -7853,13 +7591,13 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -7868,30 +7606,30 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>92.86</v>
-      </c>
-      <c r="G5">
-        <v>7.14</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2.4</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -7900,24 +7638,24 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="G6">
-        <v>4.76</v>
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.4</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7937,10 +7675,10 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
@@ -7949,7 +7687,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7969,19 +7707,19 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8026,749 +7764,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920252</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920253</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920254</v>
-      </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920256</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920257</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920258</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920259</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920081</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920262</v>
-      </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>19330051920155</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920263</v>
-      </c>
-      <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920264</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920266</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920267</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920087</v>
-      </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920088</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920358</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920268</v>
-      </c>
-      <c r="B20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920091</v>
-      </c>
-      <c r="B21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920270</v>
-      </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920271</v>
-      </c>
-      <c r="B23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920272</v>
-      </c>
-      <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" t="s">
-        <v>168</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920273</v>
-      </c>
-      <c r="B25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920274</v>
-      </c>
-      <c r="B26" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>170</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920361</v>
-      </c>
-      <c r="B27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920275</v>
-      </c>
-      <c r="B28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920362</v>
-      </c>
-      <c r="B29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" t="s">
-        <v>136</v>
-      </c>
-      <c r="D29" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920276</v>
-      </c>
-      <c r="B30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920277</v>
-      </c>
-      <c r="B31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" t="s">
-        <v>138</v>
-      </c>
-      <c r="D31" t="s">
-        <v>175</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>21330051920278</v>
-      </c>
-      <c r="B32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" t="s">
-        <v>176</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>21330051420149</v>
-      </c>
-      <c r="B33" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>21330051920279</v>
-      </c>
-      <c r="B34" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" t="s">
-        <v>178</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>21330051920280</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" t="s">
-        <v>179</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>21330051920106</v>
-      </c>
-      <c r="B36" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" t="s">
-        <v>141</v>
-      </c>
-      <c r="D36" t="s">
-        <v>180</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>21330051920282</v>
-      </c>
-      <c r="B37" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" t="s">
-        <v>142</v>
-      </c>
-      <c r="D37" t="s">
-        <v>181</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>21330051920284</v>
-      </c>
-      <c r="B38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" t="s">
-        <v>182</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>21330051920285</v>
-      </c>
-      <c r="B39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>183</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>21330051920286</v>
-      </c>
-      <c r="B40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" t="s">
-        <v>184</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>20330051920358</v>
-      </c>
-      <c r="B41" t="s">
-        <v>115</v>
-      </c>
-      <c r="C41" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>21330051920287</v>
-      </c>
-      <c r="B42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D42" t="s">
-        <v>186</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
-        <v>21330051920288</v>
-      </c>
-      <c r="B43" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" t="s">
-        <v>146</v>
-      </c>
-      <c r="D43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8803,13 +7799,13 @@
         <v>21330051920253</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -8826,13 +7822,13 @@
         <v>21330051920253</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -8849,13 +7845,13 @@
         <v>21330051920088</v>
       </c>
       <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
         <v>93</v>
-      </c>
-      <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" t="s">
-        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -8872,13 +7868,13 @@
         <v>21330051920088</v>
       </c>
       <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" t="s">
-        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -8895,13 +7891,13 @@
         <v>21330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -8918,13 +7914,13 @@
         <v>21330051920257</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -8938,22 +7934,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920155</v>
+        <v>21330051920358</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8961,16 +7957,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920358</v>
+        <v>21330051920286</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -8984,47 +7980,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920286</v>
+        <v>21330051920287</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920358</v>
-      </c>
-      <c r="B11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -257,15 +257,12 @@
     <t>ARGÜELLO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -278,15 +275,12 @@
     <t>NARANJO</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -299,13 +293,10 @@
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
     <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -841,13 +832,13 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -883,13 +874,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>9</v>
@@ -930,13 +921,13 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -975,7 +966,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1019,13 +1010,13 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -1061,13 +1052,13 @@
         <v>-1</v>
       </c>
       <c r="W6">
+        <v>7</v>
+      </c>
+      <c r="X6">
+        <v>10</v>
+      </c>
+      <c r="Y6">
         <v>5</v>
-      </c>
-      <c r="X6">
-        <v>10</v>
-      </c>
-      <c r="Y6">
-        <v>6</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1108,13 +1099,13 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1153,7 +1144,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1238,13 +1229,13 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1286,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>9</v>
@@ -1327,13 +1318,13 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>8</v>
@@ -1372,10 +1363,10 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1416,13 +1407,13 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -1458,13 +1449,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1505,13 +1496,13 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1547,13 +1538,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1594,13 +1585,13 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>6</v>
@@ -1639,10 +1630,10 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>7</v>
@@ -1683,13 +1674,13 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1725,13 +1716,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>8</v>
@@ -1772,13 +1763,13 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1814,13 +1805,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -1861,13 +1852,13 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1906,10 +1897,10 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>8</v>
@@ -1950,13 +1941,13 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -1995,7 +1986,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2039,13 +2030,13 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -2081,13 +2072,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -2128,13 +2119,13 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2176,7 +2167,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>10</v>
@@ -2217,13 +2208,13 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2259,13 +2250,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2306,13 +2297,13 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2348,13 +2339,13 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2395,13 +2386,13 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -2437,13 +2428,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2484,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2532,7 +2523,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2573,13 +2564,13 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2621,7 +2612,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2662,13 +2653,13 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2704,13 +2695,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -2751,13 +2742,13 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2799,7 +2790,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -2840,13 +2831,13 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2929,13 +2920,13 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2977,7 +2968,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3018,13 +3009,13 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -3066,7 +3057,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>8</v>
@@ -3107,13 +3098,13 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3155,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>10</v>
@@ -3196,13 +3187,13 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3244,7 +3235,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>9</v>
@@ -3285,13 +3276,13 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3327,13 +3318,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>10</v>
@@ -3374,13 +3365,13 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3416,7 +3407,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3463,13 +3454,13 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3511,7 +3502,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z34">
         <v>9</v>
@@ -3552,13 +3543,13 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -3600,7 +3591,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>10</v>
@@ -3641,13 +3632,13 @@
         <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>9</v>
@@ -3683,13 +3674,13 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z36">
         <v>9</v>
@@ -3730,13 +3721,13 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -3775,10 +3766,10 @@
         <v>9</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z37">
         <v>9</v>
@@ -3819,13 +3810,13 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>9</v>
@@ -3867,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -3908,13 +3899,13 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -3997,13 +3988,13 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>9</v>
@@ -4045,7 +4036,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z40">
         <v>10</v>
@@ -4086,13 +4077,13 @@
         <v>8</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -4134,7 +4125,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z41">
         <v>5</v>
@@ -4175,13 +4166,13 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -4223,7 +4214,7 @@
         <v>9</v>
       </c>
       <c r="Y42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z42">
         <v>6</v>
@@ -4264,13 +4255,13 @@
         <v>8</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>10</v>
@@ -4306,7 +4297,7 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>9</v>
@@ -4353,13 +4344,13 @@
         <v>10</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
         <v>9</v>
@@ -4401,7 +4392,7 @@
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z44">
         <v>8</v>
@@ -4442,13 +4433,13 @@
         <v>5</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L45">
         <v>9</v>
@@ -4487,7 +4478,7 @@
         <v>6</v>
       </c>
       <c r="X45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y45">
         <v>5</v>
@@ -4653,13 +4644,13 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L4">
         <v>106.7</v>
@@ -4721,13 +4712,13 @@
         <v>96.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L5">
         <v>106.7</v>
@@ -4789,13 +4780,13 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>106.7</v>
@@ -4857,13 +4848,13 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>106.7</v>
@@ -4957,13 +4948,13 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>106.7</v>
@@ -5025,13 +5016,13 @@
         <v>96.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>106.7</v>
@@ -5093,13 +5084,13 @@
         <v>96.7</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>106.7</v>
@@ -5161,13 +5152,13 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>106.7</v>
@@ -5229,13 +5220,13 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>106.7</v>
@@ -5297,13 +5288,13 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>106.7</v>
@@ -5365,13 +5356,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>106.7</v>
@@ -5433,13 +5424,13 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>106.7</v>
@@ -5501,13 +5492,13 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>106.7</v>
@@ -5569,13 +5560,13 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>106.7</v>
@@ -5637,13 +5628,13 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>106.7</v>
@@ -5705,13 +5696,13 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>106.7</v>
@@ -5773,13 +5764,13 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>106.7</v>
@@ -5841,13 +5832,13 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>106.7</v>
@@ -5909,13 +5900,13 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>106.7</v>
@@ -5977,13 +5968,13 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>106.7</v>
@@ -6045,13 +6036,13 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>106.7</v>
@@ -6113,13 +6104,13 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>106.7</v>
@@ -6181,13 +6172,13 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>106.7</v>
@@ -6249,13 +6240,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>106.7</v>
@@ -6317,13 +6308,13 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>106.7</v>
@@ -6385,13 +6376,13 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>106.7</v>
@@ -6453,13 +6444,13 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>106.7</v>
@@ -6521,13 +6512,13 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>106.7</v>
@@ -6589,13 +6580,13 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>106.7</v>
@@ -6657,13 +6648,13 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>106.7</v>
@@ -6725,13 +6716,13 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>106.7</v>
@@ -6793,13 +6784,13 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>106.7</v>
@@ -6861,13 +6852,13 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>106.7</v>
@@ -6929,13 +6920,13 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>106.7</v>
@@ -6997,13 +6988,13 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L39">
         <v>106.7</v>
@@ -7065,13 +7056,13 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
         <v>106.7</v>
@@ -7133,13 +7124,13 @@
         <v>100</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>106.7</v>
@@ -7201,13 +7192,13 @@
         <v>100</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42">
         <v>106.7</v>
@@ -7269,13 +7260,13 @@
         <v>100</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43">
         <v>106.7</v>
@@ -7337,13 +7328,13 @@
         <v>100</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44">
         <v>106.7</v>
@@ -7405,13 +7396,13 @@
         <v>100</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45">
         <v>106.7</v>
@@ -7542,19 +7533,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="G3" s="2">
-        <v>9.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7574,19 +7565,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>90.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7682,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7764,7 +7755,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7802,16 +7793,16 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7825,10 +7816,10 @@
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7842,16 +7833,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920088</v>
+        <v>21330051920257</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7865,16 +7856,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920088</v>
+        <v>21330051920257</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -7888,22 +7879,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920251</v>
+        <v>21330051920088</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7911,16 +7902,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920257</v>
+        <v>21330051920358</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -7934,16 +7925,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920358</v>
+        <v>21330051920286</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -7957,47 +7948,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920286</v>
+        <v>21330051920287</v>
       </c>
       <c r="B9" t="s">
         <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920287</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -4623,7 +4623,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4632,10 +4632,10 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -4644,46 +4644,46 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4691,7 +4691,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4700,10 +4700,10 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>51.7</v>
       </c>
       <c r="G5">
         <v>91.40000000000001</v>
@@ -4712,46 +4712,46 @@
         <v>96.7</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="L5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="N5">
-        <v>114.3</v>
+        <v>93.5</v>
       </c>
       <c r="O5">
         <v>96.7</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4759,7 +4759,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4768,10 +4768,10 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -4780,46 +4780,46 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4827,7 +4827,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4836,10 +4836,10 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -4848,46 +4848,46 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4895,7 +4895,7 @@
         <v>17</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>62.1</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -4904,22 +4904,22 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>110</v>
+        <v>75.5</v>
       </c>
       <c r="N8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4927,7 +4927,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4936,10 +4936,10 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -4948,46 +4948,46 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4995,7 +4995,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -5004,10 +5004,10 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -5016,46 +5016,46 @@
         <v>96.7</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5063,7 +5063,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -5072,10 +5072,10 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -5084,46 +5084,46 @@
         <v>96.7</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>110</v>
+        <v>79.2</v>
       </c>
       <c r="N11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5131,7 +5131,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -5140,10 +5140,10 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -5152,46 +5152,46 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5199,7 +5199,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -5208,10 +5208,10 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -5220,46 +5220,46 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5267,7 +5267,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -5276,10 +5276,10 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>85</v>
+        <v>58.6</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -5288,46 +5288,46 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>110</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5335,7 +5335,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -5344,10 +5344,10 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -5356,46 +5356,46 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5403,7 +5403,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -5412,10 +5412,10 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -5424,46 +5424,46 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>110</v>
+        <v>79.2</v>
       </c>
       <c r="N16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5471,7 +5471,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -5480,10 +5480,10 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>85</v>
+        <v>58.6</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -5492,46 +5492,46 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>110</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5539,7 +5539,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -5548,10 +5548,10 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -5560,46 +5560,46 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5607,7 +5607,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5616,10 +5616,10 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -5628,46 +5628,46 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5675,7 +5675,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5684,10 +5684,10 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -5696,46 +5696,46 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5743,7 +5743,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -5752,10 +5752,10 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -5764,46 +5764,46 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5811,7 +5811,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5820,10 +5820,10 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -5832,46 +5832,46 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N22">
-        <v>114.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5879,7 +5879,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5888,10 +5888,10 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -5900,46 +5900,46 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5947,7 +5947,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -5956,10 +5956,10 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -5968,46 +5968,46 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6015,7 +6015,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -6024,10 +6024,10 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -6036,46 +6036,46 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6083,7 +6083,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -6092,10 +6092,10 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -6104,46 +6104,46 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6151,7 +6151,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -6160,10 +6160,10 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -6172,46 +6172,46 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6219,7 +6219,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -6228,10 +6228,10 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -6240,46 +6240,46 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6287,7 +6287,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -6296,10 +6296,10 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -6308,46 +6308,46 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6355,7 +6355,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -6364,10 +6364,10 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -6376,46 +6376,46 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6423,7 +6423,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -6432,10 +6432,10 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -6444,46 +6444,46 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6491,7 +6491,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -6500,10 +6500,10 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -6512,46 +6512,46 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>110</v>
+        <v>97.8</v>
       </c>
       <c r="J32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6559,7 +6559,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -6568,10 +6568,10 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F33">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G33">
         <v>100</v>
@@ -6580,46 +6580,46 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6627,7 +6627,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -6636,10 +6636,10 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -6648,46 +6648,46 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6695,7 +6695,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6704,10 +6704,10 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -6716,46 +6716,46 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M35">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O35">
         <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6763,7 +6763,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6772,10 +6772,10 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -6784,46 +6784,46 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M36">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6831,7 +6831,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6840,10 +6840,10 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F37">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -6852,46 +6852,46 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O37">
         <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6899,7 +6899,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6908,10 +6908,10 @@
         <v>100</v>
       </c>
       <c r="E38">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -6920,46 +6920,46 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M38">
-        <v>110</v>
+        <v>79.2</v>
       </c>
       <c r="N38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6967,7 +6967,7 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6976,10 +6976,10 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F39">
-        <v>90</v>
+        <v>62.1</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -6988,46 +6988,46 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="J39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K39">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L39">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M39">
-        <v>100</v>
+        <v>71.7</v>
       </c>
       <c r="N39">
-        <v>114.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O39">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>71.7</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7035,7 +7035,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -7044,10 +7044,10 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F40">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G40">
         <v>100</v>
@@ -7056,46 +7056,46 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M40">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O40">
         <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7103,7 +7103,7 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -7112,10 +7112,10 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F41">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -7124,46 +7124,46 @@
         <v>100</v>
       </c>
       <c r="I41">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M41">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O41">
         <v>100</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7171,7 +7171,7 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -7180,10 +7180,10 @@
         <v>100</v>
       </c>
       <c r="E42">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F42">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -7192,46 +7192,46 @@
         <v>100</v>
       </c>
       <c r="I42">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M42">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N42">
-        <v>114.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O42">
         <v>100</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -7239,7 +7239,7 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -7248,10 +7248,10 @@
         <v>100</v>
       </c>
       <c r="E43">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F43">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -7260,46 +7260,46 @@
         <v>100</v>
       </c>
       <c r="I43">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
       <c r="L43">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M43">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O43">
         <v>100</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -7307,7 +7307,7 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -7316,10 +7316,10 @@
         <v>100</v>
       </c>
       <c r="E44">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F44">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -7328,46 +7328,46 @@
         <v>100</v>
       </c>
       <c r="I44">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="L44">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M44">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O44">
         <v>100</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -7375,7 +7375,7 @@
         <v>54</v>
       </c>
       <c r="B45">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -7384,10 +7384,10 @@
         <v>100</v>
       </c>
       <c r="E45">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F45">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G45">
         <v>100</v>
@@ -7396,46 +7396,46 @@
         <v>100</v>
       </c>
       <c r="I45">
-        <v>105</v>
+        <v>97.8</v>
       </c>
       <c r="J45">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K45">
         <v>100</v>
       </c>
       <c r="L45">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M45">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="N45">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O45">
         <v>100</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -269,9 +269,6 @@
     <t>VARGAS</t>
   </si>
   <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
     <t>NARANJO</t>
   </si>
   <si>
@@ -287,9 +284,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>AMECA</t>
-  </si>
-  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
@@ -303,9 +297,6 @@
   </si>
   <si>
     <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
   </si>
 </sst>
 </file>
@@ -853,13 +844,13 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -868,10 +859,10 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -880,7 +871,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>9</v>
@@ -889,10 +880,10 @@
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -942,13 +933,13 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -957,16 +948,16 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1031,13 +1022,13 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1046,19 +1037,19 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1105,7 +1096,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1120,13 +1111,13 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1135,19 +1126,19 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1188,10 +1179,10 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>7</v>
@@ -1200,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1250,13 +1241,13 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1265,10 +1256,10 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1339,13 +1330,13 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1354,13 +1345,13 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1375,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>9</v>
@@ -1428,13 +1419,13 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1443,19 +1434,19 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1467,7 +1458,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1517,13 +1508,13 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1532,13 +1523,13 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1606,13 +1597,13 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1621,16 +1612,16 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1695,13 +1686,13 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1710,10 +1701,10 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1722,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>8</v>
@@ -1731,10 +1722,10 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1784,13 +1775,13 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1799,10 +1790,10 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1811,7 +1802,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>8</v>
@@ -1823,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1873,13 +1864,13 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1888,13 +1879,13 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1962,13 +1953,13 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1977,10 +1968,10 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2051,13 +2042,13 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2066,10 +2057,10 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2140,13 +2131,13 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2155,10 +2146,10 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2229,13 +2220,13 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2244,19 +2235,19 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2268,7 +2259,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2318,13 +2309,13 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2333,10 +2324,10 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2345,7 +2336,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2407,13 +2398,13 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2422,10 +2413,10 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2446,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2496,13 +2487,13 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2511,13 +2502,13 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2585,13 +2576,13 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2600,10 +2591,10 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2674,13 +2665,13 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2689,10 +2680,10 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2763,13 +2754,13 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2778,10 +2769,10 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2790,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>10</v>
@@ -2852,13 +2843,13 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2867,13 +2858,13 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2941,13 +2932,13 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2956,19 +2947,19 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3030,13 +3021,13 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3045,10 +3036,10 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3119,13 +3110,13 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3134,10 +3125,10 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3155,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>9</v>
@@ -3208,13 +3199,13 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3223,13 +3214,13 @@
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3297,13 +3288,13 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3312,19 +3303,19 @@
         <v>-1</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>10</v>
@@ -3386,13 +3377,13 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3401,10 +3392,10 @@
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3475,13 +3466,13 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3490,10 +3481,10 @@
         <v>-1</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3564,13 +3555,13 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3579,13 +3570,13 @@
         <v>-1</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3653,13 +3644,13 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3668,16 +3659,16 @@
         <v>-1</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3692,7 +3683,7 @@
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3742,13 +3733,13 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3757,16 +3748,16 @@
         <v>-1</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3778,7 +3769,7 @@
         <v>10</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>9</v>
@@ -3831,13 +3822,13 @@
         <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3846,19 +3837,19 @@
         <v>-1</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -3920,13 +3911,13 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3935,16 +3926,16 @@
         <v>-1</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>5</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -4009,13 +4000,13 @@
         <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -4024,10 +4015,10 @@
         <v>-1</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>8</v>
@@ -4098,13 +4089,13 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -4113,10 +4104,10 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W41">
         <v>7</v>
@@ -4125,7 +4116,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z41">
         <v>5</v>
@@ -4134,7 +4125,7 @@
         <v>8</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC41">
         <v>9</v>
@@ -4187,13 +4178,13 @@
         <v>8</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -4202,16 +4193,16 @@
         <v>-1</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W42">
         <v>7</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y42">
         <v>7</v>
@@ -4226,7 +4217,7 @@
         <v>8</v>
       </c>
       <c r="AC42">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -4276,13 +4267,13 @@
         <v>8</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4291,10 +4282,10 @@
         <v>-1</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4315,7 +4306,7 @@
         <v>9</v>
       </c>
       <c r="AC43">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -4365,13 +4356,13 @@
         <v>8</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -4380,10 +4371,10 @@
         <v>-1</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -4454,13 +4445,13 @@
         <v>8</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S45">
         <v>-1</v>
@@ -4469,10 +4460,10 @@
         <v>-1</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>6</v>
@@ -4481,7 +4472,7 @@
         <v>8</v>
       </c>
       <c r="Y45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z45">
         <v>7</v>
@@ -4493,7 +4484,7 @@
         <v>9</v>
       </c>
       <c r="AC45">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4665,13 +4656,13 @@
         <v>98.3</v>
       </c>
       <c r="P4">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4683,7 +4674,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4733,13 +4724,13 @@
         <v>96.7</v>
       </c>
       <c r="P5">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>82.5</v>
+        <v>54.7</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4748,7 +4739,7 @@
         <v>66</v>
       </c>
       <c r="U5">
-        <v>93.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V5">
         <v>96.7</v>
@@ -4801,7 +4792,7 @@
         <v>98.3</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4816,10 +4807,10 @@
         <v>83</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V6">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -5055,7 +5046,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5105,7 +5096,7 @@
         <v>98.3</v>
       </c>
       <c r="P11">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -5120,10 +5111,10 @@
         <v>79.2</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V11">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5173,7 +5164,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -5309,7 +5300,7 @@
         <v>98.3</v>
       </c>
       <c r="P14">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5327,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5377,7 +5368,7 @@
         <v>98.3</v>
       </c>
       <c r="P15">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5395,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5463,7 +5454,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5528,7 +5519,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5596,7 +5587,7 @@
         <v>83</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5868,7 +5859,7 @@
         <v>83</v>
       </c>
       <c r="U22">
-        <v>97.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -6533,7 +6524,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6548,7 +6539,7 @@
         <v>83</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6616,7 +6607,7 @@
         <v>83</v>
       </c>
       <c r="U33">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -7009,13 +7000,13 @@
         <v>96.7</v>
       </c>
       <c r="P39">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Q39">
         <v>100</v>
       </c>
       <c r="R39">
-        <v>85</v>
+        <v>60.9</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -7024,10 +7015,10 @@
         <v>71.7</v>
       </c>
       <c r="U39">
-        <v>97.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V39">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7077,7 +7068,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -7092,7 +7083,7 @@
         <v>83</v>
       </c>
       <c r="U40">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -7145,7 +7136,7 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -7213,7 +7204,7 @@
         <v>100</v>
       </c>
       <c r="P42">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="Q42">
         <v>100</v>
@@ -7228,7 +7219,7 @@
         <v>83</v>
       </c>
       <c r="U42">
-        <v>97.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V42">
         <v>100</v>
@@ -7417,7 +7408,7 @@
         <v>100</v>
       </c>
       <c r="P45">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q45">
         <v>100</v>
@@ -7432,7 +7423,7 @@
         <v>83</v>
       </c>
       <c r="U45">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V45">
         <v>100</v>
@@ -7533,19 +7524,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>87.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>12.2</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7577,7 +7568,7 @@
         <v>4.9</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7673,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7705,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7755,7 +7746,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7793,16 +7784,16 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7810,16 +7801,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920253</v>
+        <v>21330051920257</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7833,22 +7824,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920257</v>
+        <v>21330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7856,13 +7847,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920257</v>
+        <v>21330051920358</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
         <v>91</v>
@@ -7879,13 +7870,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920088</v>
+        <v>21330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
@@ -7897,75 +7888,6 @@
         <v>67</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920358</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920286</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920287</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20222.xlsx
+++ b/grupos/4ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -257,46 +257,19 @@
     <t>ARGÜELLO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
     <t>NARANJO</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
   </si>
 </sst>
 </file>
@@ -853,10 +826,10 @@
         <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -874,10 +847,10 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>9</v>
@@ -942,10 +915,10 @@
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1031,10 +1004,10 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1120,10 +1093,10 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1176,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1250,10 +1223,10 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1339,10 +1312,10 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1360,10 +1333,10 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>9</v>
@@ -1428,10 +1401,10 @@
         <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1449,7 +1422,7 @@
         <v>6</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1517,10 +1490,10 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1538,10 +1511,10 @@
         <v>9</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1606,10 +1579,10 @@
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1630,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1695,10 +1668,10 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1716,10 +1689,10 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1784,10 +1757,10 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1805,10 +1778,10 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -1873,10 +1846,10 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -1894,10 +1867,10 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>9</v>
@@ -1962,10 +1935,10 @@
         <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1983,10 +1956,10 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2051,10 +2024,10 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2072,10 +2045,10 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -2140,10 +2113,10 @@
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2229,10 +2202,10 @@
         <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2250,7 +2223,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2318,10 +2291,10 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>10</v>
@@ -2342,7 +2315,7 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2407,10 +2380,10 @@
         <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2496,10 +2469,10 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2517,7 +2490,7 @@
         <v>9</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2585,10 +2558,10 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2674,10 +2647,10 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2763,10 +2736,10 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2852,10 +2825,10 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2873,7 +2846,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -2941,10 +2914,10 @@
         <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2965,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3030,10 +3003,10 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -3051,10 +3024,10 @@
         <v>8</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3119,10 +3092,10 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3140,7 +3113,7 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3208,10 +3181,10 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3229,7 +3202,7 @@
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3297,10 +3270,10 @@
         <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3318,10 +3291,10 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>8</v>
@@ -3386,10 +3359,10 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3407,10 +3380,10 @@
         <v>6</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>8</v>
@@ -3475,10 +3448,10 @@
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3564,10 +3537,10 @@
         <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3653,10 +3626,10 @@
         <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>10</v>
@@ -3742,10 +3715,10 @@
         <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3766,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB37">
         <v>9</v>
@@ -3831,10 +3804,10 @@
         <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -3920,10 +3893,10 @@
         <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3944,7 +3917,7 @@
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB39">
         <v>7</v>
@@ -4009,10 +3982,10 @@
         <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -4030,10 +4003,10 @@
         <v>6</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB40">
         <v>9</v>
@@ -4098,10 +4071,10 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>10</v>
@@ -4119,10 +4092,10 @@
         <v>7</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB41">
         <v>9</v>
@@ -4187,10 +4160,10 @@
         <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U42">
         <v>9</v>
@@ -4211,7 +4184,7 @@
         <v>6</v>
       </c>
       <c r="AA42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB42">
         <v>8</v>
@@ -4276,10 +4249,10 @@
         <v>7</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>10</v>
@@ -4297,7 +4270,7 @@
         <v>7</v>
       </c>
       <c r="Z43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA43">
         <v>10</v>
@@ -4365,10 +4338,10 @@
         <v>8</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U44">
         <v>10</v>
@@ -4389,7 +4362,7 @@
         <v>8</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB44">
         <v>9</v>
@@ -4454,10 +4427,10 @@
         <v>9</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U45">
         <v>9</v>
@@ -4478,7 +4451,7 @@
         <v>7</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB45">
         <v>9</v>
@@ -4668,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -4736,7 +4709,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>66</v>
+        <v>47.9</v>
       </c>
       <c r="U5">
         <v>91.09999999999999</v>
@@ -4804,7 +4777,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U6">
         <v>98.2</v>
@@ -4872,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4904,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>75.5</v>
+        <v>82.2</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -4972,7 +4945,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -5040,7 +5013,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -5108,7 +5081,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>79.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="U11">
         <v>98.2</v>
@@ -5244,7 +5217,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -5312,7 +5285,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>73.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -5380,7 +5353,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -5448,7 +5421,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>79.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -5516,7 +5489,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>73.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="U17">
         <v>98.2</v>
@@ -5584,7 +5557,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U18">
         <v>98.2</v>
@@ -5652,7 +5625,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5720,7 +5693,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -5788,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -5856,7 +5829,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U22">
         <v>98.2</v>
@@ -5924,7 +5897,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5992,7 +5965,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -6060,7 +6033,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6128,7 +6101,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -6196,7 +6169,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6264,7 +6237,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -6332,7 +6305,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -6400,7 +6373,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -6468,7 +6441,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -6536,7 +6509,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U32">
         <v>98.2</v>
@@ -6604,7 +6577,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U33">
         <v>98.2</v>
@@ -6672,7 +6645,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -6740,7 +6713,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -6808,7 +6781,7 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -6876,7 +6849,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -6944,7 +6917,7 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>79.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -7012,7 +6985,7 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>71.7</v>
+        <v>79.5</v>
       </c>
       <c r="U39">
         <v>96.40000000000001</v>
@@ -7080,7 +7053,7 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U40">
         <v>98.2</v>
@@ -7148,7 +7121,7 @@
         <v>100</v>
       </c>
       <c r="T41">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U41">
         <v>100</v>
@@ -7216,7 +7189,7 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U42">
         <v>96.40000000000001</v>
@@ -7284,7 +7257,7 @@
         <v>100</v>
       </c>
       <c r="T43">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U43">
         <v>100</v>
@@ -7352,7 +7325,7 @@
         <v>100</v>
       </c>
       <c r="T44">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U44">
         <v>100</v>
@@ -7420,7 +7393,7 @@
         <v>100</v>
       </c>
       <c r="T45">
-        <v>83</v>
+        <v>87.7</v>
       </c>
       <c r="U45">
         <v>98.2</v>
@@ -7492,19 +7465,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>82.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="G2" s="2">
-        <v>17.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7588,19 +7561,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="G5" s="2">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7746,7 +7719,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7784,10 +7757,10 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -7801,16 +7774,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920257</v>
+        <v>21330051920358</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7819,75 +7792,6 @@
         <v>67</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920088</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920358</v>
-      </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>
